--- a/data/merged/2026-09-23/MERGED_JP_Spot-Cleaner_2026-09-23.xlsx
+++ b/data/merged/2026-09-23/MERGED_JP_Spot-Cleaner_2026-09-23.xlsx
@@ -5172,13 +5172,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>43</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>43</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5216,13 +5216,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5304,13 +5304,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>46</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>46</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5348,13 +5348,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>47</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>47</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5415,94 +5415,6 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId48" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="49" name="Product 49">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId49" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="50" name="Product 50">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId50" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5844,7 +5756,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR51"/>
+  <dimension ref="A1:BR49"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -10611,7 +10523,7 @@
       <c r="B43" s="11"/>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>B0H7B99X6W</t>
+          <t>B0H89ZR9LV</t>
         </is>
       </c>
       <c r="D43" s="12"/>
@@ -10624,23 +10536,23 @@
       </c>
       <c r="H43" s="12" t="inlineStr">
         <is>
-          <t>【Amazon限定セット】±0 スチームクリーナー キッチンまわり徹底掃除セット スポンジブラシ10枚＋スポットブラシ5個＋金属ブラシ3個付き (ブラウングレー)</t>
+          <t>GOBOT 蒸汽清洁器 20秒待机 蒸汽拖把 可调节蒸汽量 轻量 地板清洁 高温蒸汽 清洁 水擦拭 蒸汽吸尘器 厨房清洁</t>
         </is>
       </c>
       <c r="I43" s="12"/>
       <c r="J43" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0H7B99X6W?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0H89ZR9LV?psc=1</t>
         </is>
       </c>
       <c r="K43" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/71TiWeA5AQL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/61eZDbDty9L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L43" s="12" t="inlineStr">
         <is>
-          <t>B0H7B99X6W</t>
+          <t>B0H89ZR9LV</t>
         </is>
       </c>
       <c r="M43" s="1"/>
@@ -10661,11 +10573,11 @@
       <c r="AB43"/>
       <c r="AC43"/>
       <c r="AD43" s="17">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AE43"/>
       <c r="AF43" s="18">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AG43" s="19">
         <v>0</v>
@@ -10717,7 +10629,7 @@
       <c r="B44" s="11"/>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>B0H89ZR9LV</t>
+          <t>B0H9L85454</t>
         </is>
       </c>
       <c r="D44" s="12"/>
@@ -10730,23 +10642,23 @@
       </c>
       <c r="H44" s="12" t="inlineStr">
         <is>
-          <t>GOBOT 蒸汽清洁器 20秒待机 蒸汽拖把 可调节蒸汽量 轻量 地板清洁 高温蒸汽 清洁 水擦拭 蒸汽吸尘器 厨房清洁</t>
+          <t>KOJIHOMU 布制品清洁剂 地毯清洁剂s自動洗浄機能 PSE認証済み 2-in-1大容量水タンク 清水汚水分離 布製品 カーペット ソファ マットレス ペットシート カーテン ぬいぐるみ 車内対応 掃除用品 收納便利 コンパクト</t>
         </is>
       </c>
       <c r="I44" s="12"/>
       <c r="J44" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0H89ZR9LV?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0H9L85454?psc=1</t>
         </is>
       </c>
       <c r="K44" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/61eZDbDty9L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/71FEf2vtKlL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L44" s="12" t="inlineStr">
         <is>
-          <t>B0H89ZR9LV</t>
+          <t>B0H9L85454</t>
         </is>
       </c>
       <c r="M44" s="1"/>
@@ -10767,7 +10679,7 @@
       <c r="AB44"/>
       <c r="AC44"/>
       <c r="AD44" s="17">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE44"/>
       <c r="AF44" s="18">
@@ -10823,7 +10735,7 @@
       <c r="B45" s="11"/>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>B0H8SPVHVZ</t>
+          <t>B0HB3GBZXD</t>
         </is>
       </c>
       <c r="D45" s="12"/>
@@ -10836,23 +10748,23 @@
       </c>
       <c r="H45" s="12" t="inlineStr">
         <is>
-          <t>【12秒速熱・大容量タンク】evove スチームクリーナー 120℃高温 高圧 ハンディタイプ 1500W 除菌率99.9% 水タンク1250ml 8種ノズル付き 油汚れ ペット 赤ちゃん おもちゃ 年末清掃 SC01</t>
+          <t>uwant B400蒸汽清洁器 【100℃蒸汽+60℃加热+18000Pa超强吸力】加热式冲洗吸尘器 家用地毯清洁剂 二合一大容量水箱干湿两用吸尘器 附带5种专用刷子和专用清洗液1个 仅更换・无需维修 布制品/织物/床垫/宠物垫/毛绒玩具/清扫用品</t>
         </is>
       </c>
       <c r="I45" s="12"/>
       <c r="J45" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0H8SPVHVZ?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0HB3GBZXD?psc=1</t>
         </is>
       </c>
       <c r="K45" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/713T4iGsd3L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/812YbgaOulL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L45" s="12" t="inlineStr">
         <is>
-          <t>B0H8SPVHVZ</t>
+          <t>B0HB3GBZXD</t>
         </is>
       </c>
       <c r="M45" s="1"/>
@@ -10873,7 +10785,7 @@
       <c r="AB45"/>
       <c r="AC45"/>
       <c r="AD45" s="17">
-        <v>20</v>
+        <v>245</v>
       </c>
       <c r="AE45"/>
       <c r="AF45" s="18">
@@ -10929,7 +10841,7 @@
       <c r="B46" s="11"/>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>B0H9L85454</t>
+          <t>B0HCXYP8HJ</t>
         </is>
       </c>
       <c r="D46" s="12"/>
@@ -10942,23 +10854,23 @@
       </c>
       <c r="H46" s="12" t="inlineStr">
         <is>
-          <t>KOJIHOMU 布制品清洁剂 地毯清洁剂s自動洗浄機能 PSE認証済み 2-in-1大容量水タンク 清水汚水分離 布製品 カーペット ソファ マットレス ペットシート カーテン ぬいぐるみ 車内対応 掃除用品 收納便利 コンパクト</t>
+          <t>SOLVIA 蒸汽清洁器 冲洗式吸尘器 100°C 水温蒸汽 20000Pa 强吸力 清洗机 宠物 污渍 异味 车内 清洁 沙发 地毯 布制品 织物 清洁 静音设计 大容量水箱 自清洁 收纳袋 带布 4合1 多功能 油污 水垢 去污 毛绒玩具 厨房</t>
         </is>
       </c>
       <c r="I46" s="12"/>
       <c r="J46" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0H9L85454?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0HCXYP8HJ?psc=1</t>
         </is>
       </c>
       <c r="K46" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/71FEf2vtKlL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/71X6+LfqdML._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L46" s="12" t="inlineStr">
         <is>
-          <t>B0H9L85454</t>
+          <t>B0HCXYP8HJ</t>
         </is>
       </c>
       <c r="M46" s="1"/>
@@ -10979,11 +10891,11 @@
       <c r="AB46"/>
       <c r="AC46"/>
       <c r="AD46" s="17">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AE46"/>
       <c r="AF46" s="18">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AG46" s="19">
         <v>0</v>
@@ -11035,7 +10947,7 @@
       <c r="B47" s="11"/>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>B0HB3GBZXD</t>
+          <t>B0HDNVDFD6</t>
         </is>
       </c>
       <c r="D47" s="12"/>
@@ -11048,23 +10960,23 @@
       </c>
       <c r="H47" s="12" t="inlineStr">
         <is>
-          <t>uwant B400蒸汽清洁器 【100℃蒸汽+60℃加热+18000Pa超强吸力】加热式冲洗吸尘器 家用地毯清洁剂 二合一大容量水箱干湿两用吸尘器 附带5种专用刷子和专用清洗液1个 仅更换・无需维修 布制品/织物/床垫/宠物垫/毛绒玩具/清扫用品</t>
+          <t>Yadea S-Max Ultra 蒸汽式地毯清洁器s蒸汽清洗,地毯可用</t>
         </is>
       </c>
       <c r="I47" s="12"/>
       <c r="J47" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0HB3GBZXD?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0HDNVDFD6?psc=1</t>
         </is>
       </c>
       <c r="K47" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/812YbgaOulL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/71DUnGhQ+7L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L47" s="12" t="inlineStr">
         <is>
-          <t>B0HB3GBZXD</t>
+          <t>B0HDNVDFD6</t>
         </is>
       </c>
       <c r="M47" s="1"/>
@@ -11084,13 +10996,9 @@
       <c r="AA47"/>
       <c r="AB47"/>
       <c r="AC47"/>
-      <c r="AD47" s="17">
-        <v>245</v>
-      </c>
+      <c r="AD47" s="17"/>
       <c r="AE47"/>
-      <c r="AF47" s="18">
-        <v>4.4</v>
-      </c>
+      <c r="AF47" s="18"/>
       <c r="AG47" s="19">
         <v>0</v>
       </c>
@@ -11141,7 +11049,7 @@
       <c r="B48" s="11"/>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>B0HCXYP8HJ</t>
+          <t>B0HGDW31K7</t>
         </is>
       </c>
       <c r="D48" s="12"/>
@@ -11154,23 +11062,23 @@
       </c>
       <c r="H48" s="12" t="inlineStr">
         <is>
-          <t>SOLVIA 蒸汽清洁器 冲洗式吸尘器 100°C 水温蒸汽 20000Pa 强吸力 清洗机 宠物 污渍 异味 车内 清洁 沙发 地毯 布制品 织物 清洁 静音设计 大容量水箱 自清洁 收纳袋 带布 4合1 多功能 油污 水垢 去污 毛绒玩具 厨房</t>
+          <t>[Yarycop] 吸力式 蒸汽清洁器 TURBO2 Turbo 2 100℃的蒸汽可灭99.9% 除菌、99.9% 除螨 压倒性的清洁力 冲洗清洁车 宠物清洁剂 (深灰色)</t>
         </is>
       </c>
       <c r="I48" s="12"/>
       <c r="J48" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0HCXYP8HJ?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0HGDW31K7?psc=1</t>
         </is>
       </c>
       <c r="K48" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/71X6+LfqdML._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/716XZ1MWFaL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L48" s="12" t="inlineStr">
         <is>
-          <t>B0HCXYP8HJ</t>
+          <t>B0HGDW31K7</t>
         </is>
       </c>
       <c r="M48" s="1"/>
@@ -11191,11 +11099,11 @@
       <c r="AB48"/>
       <c r="AC48"/>
       <c r="AD48" s="17">
-        <v>12</v>
+        <v>118</v>
       </c>
       <c r="AE48"/>
       <c r="AF48" s="18">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AG48" s="19">
         <v>0</v>
@@ -11247,7 +11155,7 @@
       <c r="B49" s="11"/>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>B0HDNVDFD6</t>
+          <t>B0HK3489BN</t>
         </is>
       </c>
       <c r="D49" s="12"/>
@@ -11260,23 +11168,23 @@
       </c>
       <c r="H49" s="12" t="inlineStr">
         <is>
-          <t>Yadea S-Max Ultra 蒸汽式地毯清洁器s蒸汽清洗,地毯可用</t>
+          <t>Waitbird 120℃高温蒸気除菌 ハンドスチームクリーナーs21 点アクセサリー付き｜4.5Bar 高圧｜5 分速熱｜1.1L 大容量タンク｜二重安全ロック｜薬剤不要 カーペット・ソファ・車内・マットレス・キッチン掃除対応</t>
         </is>
       </c>
       <c r="I49" s="12"/>
       <c r="J49" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0HDNVDFD6?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0HK3489BN?psc=1</t>
         </is>
       </c>
       <c r="K49" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/71DUnGhQ+7L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/61ms9MUfEaL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L49" s="12" t="inlineStr">
         <is>
-          <t>B0HDNVDFD6</t>
+          <t>B0HK3489BN</t>
         </is>
       </c>
       <c r="M49" s="1"/>
@@ -11296,9 +11204,13 @@
       <c r="AA49"/>
       <c r="AB49"/>
       <c r="AC49"/>
-      <c r="AD49" s="17"/>
+      <c r="AD49" s="17">
+        <v>24</v>
+      </c>
       <c r="AE49"/>
-      <c r="AF49" s="18"/>
+      <c r="AF49" s="18">
+        <v>5</v>
+      </c>
       <c r="AG49" s="19">
         <v>0</v>
       </c>
@@ -11341,218 +11253,6 @@
       <c r="BP49"/>
       <c r="BQ49" s="20"/>
       <c r="BR49"/>
-    </row>
-    <row r="50" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="11">
-        <v>49</v>
-      </c>
-      <c r="B50" s="11"/>
-      <c r="C50" s="12" t="inlineStr">
-        <is>
-          <t>B0HGDW31K7</t>
-        </is>
-      </c>
-      <c r="D50" s="12"/>
-      <c r="E50" s="12"/>
-      <c r="F50"/>
-      <c r="G50" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jpundefined</t>
-        </is>
-      </c>
-      <c r="H50" s="12" t="inlineStr">
-        <is>
-          <t>[Yarycop] 吸力式 蒸汽清洁器 TURBO2 Turbo 2 100℃的蒸汽可灭99.9% 除菌、99.9% 除螨 压倒性的清洁力 冲洗清洁车 宠物清洁剂 (深灰色)</t>
-        </is>
-      </c>
-      <c r="I50" s="12"/>
-      <c r="J50" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B0HGDW31K7?psc=1</t>
-        </is>
-      </c>
-      <c r="K50" s="12" t="inlineStr">
-        <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/716XZ1MWFaL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L50" s="12" t="inlineStr">
-        <is>
-          <t>B0HGDW31K7</t>
-        </is>
-      </c>
-      <c r="M50" s="1"/>
-      <c r="N50" s="12"/>
-      <c r="O50" s="13"/>
-      <c r="P50" s="13"/>
-      <c r="Q50" s="14"/>
-      <c r="R50" s="15"/>
-      <c r="S50" s="16"/>
-      <c r="T50" s="13"/>
-      <c r="U50" s="14"/>
-      <c r="V50" s="13"/>
-      <c r="W50" s="13"/>
-      <c r="X50" s="13"/>
-      <c r="Y50"/>
-      <c r="Z50" s="2"/>
-      <c r="AA50"/>
-      <c r="AB50"/>
-      <c r="AC50"/>
-      <c r="AD50" s="17">
-        <v>118</v>
-      </c>
-      <c r="AE50"/>
-      <c r="AF50" s="18">
-        <v>4</v>
-      </c>
-      <c r="AG50" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH50"/>
-      <c r="AI50" s="14">
-        <v>0</v>
-      </c>
-      <c r="AJ50"/>
-      <c r="AK50" s="1"/>
-      <c r="AL50" s="17"/>
-      <c r="AM50"/>
-      <c r="AN50" s="11"/>
-      <c r="AO50" s="11"/>
-      <c r="AP50"/>
-      <c r="AQ50" s="17"/>
-      <c r="AR50"/>
-      <c r="AS50"/>
-      <c r="AT50"/>
-      <c r="AU50" s="11"/>
-      <c r="AV50" s="12"/>
-      <c r="AW50" s="11"/>
-      <c r="AX50" s="11"/>
-      <c r="AY50" s="11"/>
-      <c r="AZ50" s="11"/>
-      <c r="BA50" s="11"/>
-      <c r="BB50" s="11"/>
-      <c r="BC50" s="11"/>
-      <c r="BD50" s="11"/>
-      <c r="BE50" s="11"/>
-      <c r="BF50" s="11"/>
-      <c r="BG50" s="11"/>
-      <c r="BH50" s="12"/>
-      <c r="BI50"/>
-      <c r="BJ50"/>
-      <c r="BK50" s="20"/>
-      <c r="BL50"/>
-      <c r="BM50" s="20"/>
-      <c r="BN50"/>
-      <c r="BO50" s="20"/>
-      <c r="BP50"/>
-      <c r="BQ50" s="20"/>
-      <c r="BR50"/>
-    </row>
-    <row r="51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="11">
-        <v>50</v>
-      </c>
-      <c r="B51" s="11"/>
-      <c r="C51" s="12" t="inlineStr">
-        <is>
-          <t>B0HK3489BN</t>
-        </is>
-      </c>
-      <c r="D51" s="12"/>
-      <c r="E51" s="12"/>
-      <c r="F51"/>
-      <c r="G51" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jpundefined</t>
-        </is>
-      </c>
-      <c r="H51" s="12" t="inlineStr">
-        <is>
-          <t>Waitbird 120℃高温蒸気除菌 ハンドスチームクリーナーs21 点アクセサリー付き｜4.5Bar 高圧｜5 分速熱｜1.1L 大容量タンク｜二重安全ロック｜薬剤不要 カーペット・ソファ・車内・マットレス・キッチン掃除対応</t>
-        </is>
-      </c>
-      <c r="I51" s="12"/>
-      <c r="J51" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B0HK3489BN?psc=1</t>
-        </is>
-      </c>
-      <c r="K51" s="12" t="inlineStr">
-        <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/61ms9MUfEaL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L51" s="12" t="inlineStr">
-        <is>
-          <t>B0HK3489BN</t>
-        </is>
-      </c>
-      <c r="M51" s="1"/>
-      <c r="N51" s="12"/>
-      <c r="O51" s="13"/>
-      <c r="P51" s="13"/>
-      <c r="Q51" s="14"/>
-      <c r="R51" s="15"/>
-      <c r="S51" s="16"/>
-      <c r="T51" s="13"/>
-      <c r="U51" s="14"/>
-      <c r="V51" s="13"/>
-      <c r="W51" s="13"/>
-      <c r="X51" s="13"/>
-      <c r="Y51"/>
-      <c r="Z51" s="2"/>
-      <c r="AA51"/>
-      <c r="AB51"/>
-      <c r="AC51"/>
-      <c r="AD51" s="17">
-        <v>24</v>
-      </c>
-      <c r="AE51"/>
-      <c r="AF51" s="18">
-        <v>5</v>
-      </c>
-      <c r="AG51" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH51"/>
-      <c r="AI51" s="14">
-        <v>0</v>
-      </c>
-      <c r="AJ51"/>
-      <c r="AK51" s="1"/>
-      <c r="AL51" s="17"/>
-      <c r="AM51"/>
-      <c r="AN51" s="11"/>
-      <c r="AO51" s="11"/>
-      <c r="AP51"/>
-      <c r="AQ51" s="17"/>
-      <c r="AR51"/>
-      <c r="AS51"/>
-      <c r="AT51"/>
-      <c r="AU51" s="11"/>
-      <c r="AV51" s="12"/>
-      <c r="AW51" s="11"/>
-      <c r="AX51" s="11"/>
-      <c r="AY51" s="11"/>
-      <c r="AZ51" s="11"/>
-      <c r="BA51" s="11"/>
-      <c r="BB51" s="11"/>
-      <c r="BC51" s="11"/>
-      <c r="BD51" s="11"/>
-      <c r="BE51" s="11"/>
-      <c r="BF51" s="11"/>
-      <c r="BG51" s="11"/>
-      <c r="BH51" s="12"/>
-      <c r="BI51"/>
-      <c r="BJ51"/>
-      <c r="BK51" s="20"/>
-      <c r="BL51"/>
-      <c r="BM51" s="20"/>
-      <c r="BN51"/>
-      <c r="BO51" s="20"/>
-      <c r="BP51"/>
-      <c r="BQ51" s="20"/>
-      <c r="BR51"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11763,53 +11463,43 @@
     <hyperlink ref="J42" r:id="rId203" tooltip="https://www.amazon.co.jp/dp/B0H71G8T16?psc=1"/>
     <hyperlink ref="K42" r:id="rId204" tooltip="https://images-fe.ssl-images-amazon.com/images/I/71nyN3+jhYL._AC_UL300_SR300,200_.jpg"/>
     <hyperlink ref="L42" r:id="rId205" tooltip="https://www.amazon.co.jp/dp/B0H71G8T16"/>
-    <hyperlink ref="C43" r:id="rId206" tooltip="https://www.amazon.co.jp/dp/B0H7B99X6W"/>
+    <hyperlink ref="C43" r:id="rId206" tooltip="https://www.amazon.co.jp/dp/B0H89ZR9LV"/>
     <hyperlink ref="G43" r:id="rId207" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J43" r:id="rId208" tooltip="https://www.amazon.co.jp/dp/B0H7B99X6W?psc=1"/>
-    <hyperlink ref="K43" r:id="rId209" tooltip="https://images-fe.ssl-images-amazon.com/images/I/71TiWeA5AQL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L43" r:id="rId210" tooltip="https://www.amazon.co.jp/dp/B0H7B99X6W"/>
-    <hyperlink ref="C44" r:id="rId211" tooltip="https://www.amazon.co.jp/dp/B0H89ZR9LV"/>
+    <hyperlink ref="J43" r:id="rId208" tooltip="https://www.amazon.co.jp/dp/B0H89ZR9LV?psc=1"/>
+    <hyperlink ref="K43" r:id="rId209" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61eZDbDty9L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L43" r:id="rId210" tooltip="https://www.amazon.co.jp/dp/B0H89ZR9LV"/>
+    <hyperlink ref="C44" r:id="rId211" tooltip="https://www.amazon.co.jp/dp/B0H9L85454"/>
     <hyperlink ref="G44" r:id="rId212" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J44" r:id="rId213" tooltip="https://www.amazon.co.jp/dp/B0H89ZR9LV?psc=1"/>
-    <hyperlink ref="K44" r:id="rId214" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61eZDbDty9L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L44" r:id="rId215" tooltip="https://www.amazon.co.jp/dp/B0H89ZR9LV"/>
-    <hyperlink ref="C45" r:id="rId216" tooltip="https://www.amazon.co.jp/dp/B0H8SPVHVZ"/>
+    <hyperlink ref="J44" r:id="rId213" tooltip="https://www.amazon.co.jp/dp/B0H9L85454?psc=1"/>
+    <hyperlink ref="K44" r:id="rId214" tooltip="https://images-fe.ssl-images-amazon.com/images/I/71FEf2vtKlL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L44" r:id="rId215" tooltip="https://www.amazon.co.jp/dp/B0H9L85454"/>
+    <hyperlink ref="C45" r:id="rId216" tooltip="https://www.amazon.co.jp/dp/B0HB3GBZXD"/>
     <hyperlink ref="G45" r:id="rId217" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J45" r:id="rId218" tooltip="https://www.amazon.co.jp/dp/B0H8SPVHVZ?psc=1"/>
-    <hyperlink ref="K45" r:id="rId219" tooltip="https://images-fe.ssl-images-amazon.com/images/I/713T4iGsd3L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L45" r:id="rId220" tooltip="https://www.amazon.co.jp/dp/B0H8SPVHVZ"/>
-    <hyperlink ref="C46" r:id="rId221" tooltip="https://www.amazon.co.jp/dp/B0H9L85454"/>
+    <hyperlink ref="J45" r:id="rId218" tooltip="https://www.amazon.co.jp/dp/B0HB3GBZXD?psc=1"/>
+    <hyperlink ref="K45" r:id="rId219" tooltip="https://images-fe.ssl-images-amazon.com/images/I/812YbgaOulL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L45" r:id="rId220" tooltip="https://www.amazon.co.jp/dp/B0HB3GBZXD"/>
+    <hyperlink ref="C46" r:id="rId221" tooltip="https://www.amazon.co.jp/dp/B0HCXYP8HJ"/>
     <hyperlink ref="G46" r:id="rId222" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J46" r:id="rId223" tooltip="https://www.amazon.co.jp/dp/B0H9L85454?psc=1"/>
-    <hyperlink ref="K46" r:id="rId224" tooltip="https://images-fe.ssl-images-amazon.com/images/I/71FEf2vtKlL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L46" r:id="rId225" tooltip="https://www.amazon.co.jp/dp/B0H9L85454"/>
-    <hyperlink ref="C47" r:id="rId226" tooltip="https://www.amazon.co.jp/dp/B0HB3GBZXD"/>
+    <hyperlink ref="J46" r:id="rId223" tooltip="https://www.amazon.co.jp/dp/B0HCXYP8HJ?psc=1"/>
+    <hyperlink ref="K46" r:id="rId224" tooltip="https://images-fe.ssl-images-amazon.com/images/I/71X6+LfqdML._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L46" r:id="rId225" tooltip="https://www.amazon.co.jp/dp/B0HCXYP8HJ"/>
+    <hyperlink ref="C47" r:id="rId226" tooltip="https://www.amazon.co.jp/dp/B0HDNVDFD6"/>
     <hyperlink ref="G47" r:id="rId227" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J47" r:id="rId228" tooltip="https://www.amazon.co.jp/dp/B0HB3GBZXD?psc=1"/>
-    <hyperlink ref="K47" r:id="rId229" tooltip="https://images-fe.ssl-images-amazon.com/images/I/812YbgaOulL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L47" r:id="rId230" tooltip="https://www.amazon.co.jp/dp/B0HB3GBZXD"/>
-    <hyperlink ref="C48" r:id="rId231" tooltip="https://www.amazon.co.jp/dp/B0HCXYP8HJ"/>
+    <hyperlink ref="J47" r:id="rId228" tooltip="https://www.amazon.co.jp/dp/B0HDNVDFD6?psc=1"/>
+    <hyperlink ref="K47" r:id="rId229" tooltip="https://images-fe.ssl-images-amazon.com/images/I/71DUnGhQ+7L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L47" r:id="rId230" tooltip="https://www.amazon.co.jp/dp/B0HDNVDFD6"/>
+    <hyperlink ref="C48" r:id="rId231" tooltip="https://www.amazon.co.jp/dp/B0HGDW31K7"/>
     <hyperlink ref="G48" r:id="rId232" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J48" r:id="rId233" tooltip="https://www.amazon.co.jp/dp/B0HCXYP8HJ?psc=1"/>
-    <hyperlink ref="K48" r:id="rId234" tooltip="https://images-fe.ssl-images-amazon.com/images/I/71X6+LfqdML._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L48" r:id="rId235" tooltip="https://www.amazon.co.jp/dp/B0HCXYP8HJ"/>
-    <hyperlink ref="C49" r:id="rId236" tooltip="https://www.amazon.co.jp/dp/B0HDNVDFD6"/>
+    <hyperlink ref="J48" r:id="rId233" tooltip="https://www.amazon.co.jp/dp/B0HGDW31K7?psc=1"/>
+    <hyperlink ref="K48" r:id="rId234" tooltip="https://images-fe.ssl-images-amazon.com/images/I/716XZ1MWFaL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L48" r:id="rId235" tooltip="https://www.amazon.co.jp/dp/B0HGDW31K7"/>
+    <hyperlink ref="C49" r:id="rId236" tooltip="https://www.amazon.co.jp/dp/B0HK3489BN"/>
     <hyperlink ref="G49" r:id="rId237" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J49" r:id="rId238" tooltip="https://www.amazon.co.jp/dp/B0HDNVDFD6?psc=1"/>
-    <hyperlink ref="K49" r:id="rId239" tooltip="https://images-fe.ssl-images-amazon.com/images/I/71DUnGhQ+7L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L49" r:id="rId240" tooltip="https://www.amazon.co.jp/dp/B0HDNVDFD6"/>
-    <hyperlink ref="C50" r:id="rId241" tooltip="https://www.amazon.co.jp/dp/B0HGDW31K7"/>
-    <hyperlink ref="G50" r:id="rId242" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J50" r:id="rId243" tooltip="https://www.amazon.co.jp/dp/B0HGDW31K7?psc=1"/>
-    <hyperlink ref="K50" r:id="rId244" tooltip="https://images-fe.ssl-images-amazon.com/images/I/716XZ1MWFaL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L50" r:id="rId245" tooltip="https://www.amazon.co.jp/dp/B0HGDW31K7"/>
-    <hyperlink ref="C51" r:id="rId246" tooltip="https://www.amazon.co.jp/dp/B0HK3489BN"/>
-    <hyperlink ref="G51" r:id="rId247" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J51" r:id="rId248" tooltip="https://www.amazon.co.jp/dp/B0HK3489BN?psc=1"/>
-    <hyperlink ref="K51" r:id="rId249" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61ms9MUfEaL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L51" r:id="rId250" tooltip="https://www.amazon.co.jp/dp/B0HK3489BN"/>
+    <hyperlink ref="J49" r:id="rId238" tooltip="https://www.amazon.co.jp/dp/B0HK3489BN?psc=1"/>
+    <hyperlink ref="K49" r:id="rId239" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61ms9MUfEaL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L49" r:id="rId240" tooltip="https://www.amazon.co.jp/dp/B0HK3489BN"/>
   </hyperlinks>
-  <drawing r:id="rId251"/>
+  <drawing r:id="rId241"/>
 </worksheet>
 </file>
 
